--- a/out/MLP-S4_repeat_3_000007.xlsx
+++ b/out/MLP-S4_repeat_3_000007.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.9110100759941124</v>
+        <v>1.305315212968727</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>3.50780289896909</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.3110100759941124</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.3110100759941124</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.9110100759941124</v>
+        <v>1.305315212968727</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.9209439647931161</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.9209439647931161</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.9110100759941124</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.9209439647931161</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.9209439647931161</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.9110100759941124</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.9209439647931161</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.9209439647931161</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.9110100759941124</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.9110100759941124</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>3.50780289896909</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.3110100759941124</v>
+        <v>-0.9209439647931161</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.3110100759941124</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.9110100759941124</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.9110100759941124</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.9209439647931161</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.9110100759941124</v>
+        <v>1.305315212968727</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA30" t="n">
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.9110100759941124</v>
+        <v>1.305315212968727</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.9110100759941124</v>
+        <v>1.305315212968727</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.9209439647931161</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.9110100759941124</v>
+        <v>1.305315212968727</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.9110100759941124</v>
+        <v>1.305315212968727</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>3.50780289896909</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>3.50780289896909</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>3.50780289896909</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,10 +31949,10 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>3.50780289896909</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC39" t="n">
-        <v>-0.0003674984412823105</v>
+        <v>-0.0002452957472699927</v>
       </c>
     </row>
     <row r="40">
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>4.236714191927718</v>
+        <v>2.827897611773278</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
@@ -32744,10 +32744,10 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>3.50780289896909</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC40" t="n">
-        <v>8.479977730957103</v>
+        <v>5.660166794462667</v>
       </c>
     </row>
     <row r="41">
@@ -33528,7 +33528,7 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.635314214801281</v>
+        <v>0.424055884192473</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
@@ -33539,10 +33539,10 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>3.50780289896909</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC41" t="n">
-        <v>5.508205563908311</v>
+        <v>3.676585371983977</v>
       </c>
     </row>
     <row r="42">
@@ -34323,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.7943494296378657</v>
+        <v>0.5302078341021269</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
@@ -34331,13 +34331,13 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.3110100759941124</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC42" t="n">
-        <v>6.461691214287085</v>
+        <v>4.313012499027483</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>1.138696140261829</v>
+        <v>0.7600504157268875</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35129,10 +35129,10 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>2.90780289896909</v>
+        <v>1.305315212968727</v>
       </c>
       <c r="JC43" t="n">
-        <v>7.945182563901387</v>
+        <v>5.303204716127347</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>1.218179665453335</v>
+        <v>0.8131033942047913</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>2.90780289896909</v>
+        <v>1.305315212968727</v>
       </c>
       <c r="JC44" t="n">
-        <v>9.242930328358025</v>
+        <v>6.169417756802826</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>1.291024172150352</v>
+        <v>0.8617249715308376</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>3.50780289896909</v>
+        <v>1.305315212968727</v>
       </c>
       <c r="JC45" t="n">
-        <v>10.60689266345952</v>
+        <v>7.079827309796583</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.5826151974237787</v>
+        <v>0.3888811184859731</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>3.50780289896909</v>
+        <v>1.305315212968727</v>
       </c>
       <c r="JC46" t="n">
-        <v>10.480025906215</v>
+        <v>6.995147008490556</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.2813771541925718</v>
+        <v>0.1878111626553322</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC47" t="n">
-        <v>10.45970683448137</v>
+        <v>6.981584566681281</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.1340672239460708</v>
+        <v>0.08948642751101747</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>2.90780289896909</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC48" t="n">
-        <v>10.44624190243252</v>
+        <v>6.972597050322197</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.03972318327363588</v>
+        <v>0.02651456745518518</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.9110100759941124</v>
+        <v>1.305315212968727</v>
       </c>
       <c r="JC49" t="n">
-        <v>10.39147773795493</v>
+        <v>6.936043210671892</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.02627540443743448</v>
+        <v>0.01753839762965353</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.9110100759941124</v>
+        <v>1.305315212968727</v>
       </c>
       <c r="JC50" t="n">
-        <v>10.40428485737099</v>
+        <v>6.944591594130808</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.01344763436557187</v>
+        <v>0.008973590446594742</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC51" t="n">
-        <v>10.40488512594918</v>
+        <v>6.944990586714146</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.006876542371678241</v>
+        <v>0.004588399333231102</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC52" t="n">
-        <v>10.40518257374426</v>
+        <v>6.94518746929006</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.002582032646931447</v>
+        <v>0.001721454496094392</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC53" t="n">
-        <v>10.40346488316397</v>
+        <v>6.94403925630647</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.001404935215134951</v>
+        <v>0.0009363318200520654</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC54" t="n">
-        <v>10.40369127978369</v>
+        <v>6.944188746384352</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0006736993777768125</v>
+        <v>0.0004479960718182472</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.9110100759941124</v>
+        <v>1.305315212968727</v>
       </c>
       <c r="JC55" t="n">
-        <v>10.40363364700469</v>
+        <v>6.944148606697292</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.0004151488351447622</v>
+        <v>0.0002754272084689864</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.9110100759941124</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC56" t="n">
-        <v>10.40379011738283</v>
+        <v>6.944251442669252</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.0002152849997018866</v>
+        <v>0.0001421997895204196</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.9209439647931161</v>
       </c>
       <c r="JC57" t="n">
-        <v>10.40380430991044</v>
+        <v>6.944259267582559</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.000101902964994014</v>
+        <v>6.593561228574761e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>3.50780289896909</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC58" t="n">
-        <v>10.40379269293151</v>
+        <v>6.944249846564512</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>6.279475802142372e-05</v>
+        <v>4.104926959945762e-05</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>3.50780289896909</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC59" t="n">
-        <v>10.40381761234375</v>
+        <v>6.944264978730758</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>2.647150449619047e-05</v>
+        <v>1.598100299746031e-05</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.3110100759941124</v>
+        <v>-0.9209439647931161</v>
       </c>
       <c r="JC60" t="n">
-        <v>10.40380643584548</v>
+        <v>6.944255861065246</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>8.38179904731087e-06</v>
+        <v>4.264322417369065e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.3110100759941124</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC61" t="n">
-        <v>10.40379773660624</v>
+        <v>6.944248394488252</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>2.788397616378431e-06</v>
+        <v>-5.494870763551826e-07</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC62" t="n">
-        <v>10.40379389416601</v>
+        <v>6.944244139310081</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>-2.093548687745288e-06</v>
+        <v>-3.062365791830193e-06</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC63" t="n">
-        <v>10.40378788273942</v>
+        <v>6.944238417031051</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>-3.107779831880603e-06</v>
+        <v>-4.053889915940302e-06</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.9110100759941124</v>
+        <v>1.305315212968727</v>
       </c>
       <c r="JC64" t="n">
-        <v>10.40378278949728</v>
+        <v>6.944233347675682</v>
       </c>
     </row>
     <row r="65">
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>3.50780289896909</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC65" t="n">
-        <v>10.40377842452332</v>
+        <v>6.944228982701714</v>
       </c>
     </row>
     <row r="66">
@@ -53414,10 +53414,10 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>3.50780289896909</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC66" t="n">
-        <v>10.40377951576977</v>
+        <v>6.94423007394817</v>
       </c>
     </row>
     <row r="67">
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>3.50780289896909</v>
+        <v>-0.9209439647931161</v>
       </c>
       <c r="JC67" t="n">
-        <v>10.40377882616264</v>
+        <v>6.944229384341035</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.3110100759941124</v>
+        <v>-0.9209439647931161</v>
       </c>
       <c r="JC68" t="n">
-        <v>10.40377885647504</v>
+        <v>6.944229414653436</v>
       </c>
     </row>
     <row r="69">
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.3110100759941124</v>
+        <v>1.305315212968727</v>
       </c>
       <c r="JC69" t="n">
-        <v>10.40377866702253</v>
+        <v>6.944229225200926</v>
       </c>
     </row>
     <row r="70">
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.9110100759941124</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC70" t="n">
-        <v>10.40377872006923</v>
+        <v>6.944229278247629</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.9209439647931161</v>
       </c>
       <c r="JC71" t="n">
-        <v>10.40377877311593</v>
+        <v>6.944229331294332</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC72" t="n">
-        <v>10.40377873522543</v>
+        <v>6.944229293403829</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC73" t="n">
-        <v>10.40377860639773</v>
+        <v>6.944229164576122</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC74" t="n">
-        <v>10.40377846241382</v>
+        <v>6.944229020592215</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC75" t="n">
-        <v>10.40377830327371</v>
+        <v>6.944228861452108</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC76" t="n">
-        <v>10.40377835632041</v>
+        <v>6.94422891449881</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.9110100759941124</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC77" t="n">
-        <v>10.40377830327371</v>
+        <v>6.944228861452108</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.9209439647931161</v>
       </c>
       <c r="JC78" t="n">
-        <v>10.40377830327371</v>
+        <v>6.944228861452108</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.9110100759941124</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC79" t="n">
-        <v>10.4037781213993</v>
+        <v>6.944228679577698</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.9110100759941124</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC80" t="n">
-        <v>10.40377828811751</v>
+        <v>6.944228846295906</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.9209439647931161</v>
       </c>
       <c r="JC81" t="n">
-        <v>10.40377848514812</v>
+        <v>6.944229043326517</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.9209439647931161</v>
       </c>
       <c r="JC82" t="n">
-        <v>10.40377832600801</v>
+        <v>6.944228884186408</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC83" t="n">
-        <v>10.40377836389851</v>
+        <v>6.94422892207691</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC84" t="n">
-        <v>10.40377856092912</v>
+        <v>6.94422911910752</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC85" t="n">
-        <v>10.40377853819482</v>
+        <v>6.944229096373219</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC86" t="n">
-        <v>10.40377838663281</v>
+        <v>6.944228944811211</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.9110100759941124</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC87" t="n">
-        <v>10.40377831085181</v>
+        <v>6.944228869030208</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.9209439647931161</v>
       </c>
       <c r="JC88" t="n">
-        <v>10.40377840936711</v>
+        <v>6.944228967545513</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>1</v>
       </c>
       <c r="JB89" t="n">
-        <v>3.50780289896909</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC89" t="n">
-        <v>10.40377841694522</v>
+        <v>6.944228975123613</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.3110100759941124</v>
+        <v>-0.9209439647931161</v>
       </c>
       <c r="JC90" t="n">
-        <v>10.40377868217873</v>
+        <v>6.944229240357127</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.3110100759941124</v>
+        <v>-0.9209439647931161</v>
       </c>
       <c r="JC91" t="n">
-        <v>10.40377838663281</v>
+        <v>6.944228944811211</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.9110100759941124</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC92" t="n">
-        <v>10.40377862913203</v>
+        <v>6.944229187310424</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.9209439647931161</v>
       </c>
       <c r="JC93" t="n">
-        <v>10.40377871249113</v>
+        <v>6.944229270669529</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>3.50780289896909</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC94" t="n">
-        <v>10.40377854577292</v>
+        <v>6.94422910395132</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.3110100759941124</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC95" t="n">
-        <v>10.40377873522543</v>
+        <v>6.944229293403829</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.3110100759941124</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC96" t="n">
-        <v>10.40377838663281</v>
+        <v>6.944228944811211</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC97" t="n">
-        <v>10.4037781820241</v>
+        <v>6.944228740202501</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC98" t="n">
-        <v>10.40377829569561</v>
+        <v>6.944228853874006</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC99" t="n">
-        <v>10.40377831085181</v>
+        <v>6.944228869030208</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.9110100759941124</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC100" t="n">
-        <v>10.4037780759307</v>
+        <v>6.944228634109096</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.9209439647931161</v>
       </c>
       <c r="JC101" t="n">
-        <v>10.4037781365555</v>
+        <v>6.944228694733898</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.9209439647931161</v>
       </c>
       <c r="JC102" t="n">
-        <v>10.40377800772779</v>
+        <v>6.944228565906191</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.9110100759941124</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC103" t="n">
-        <v>10.4037781441336</v>
+        <v>6.944228702312</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.9209439647931161</v>
       </c>
       <c r="JC104" t="n">
-        <v>10.40377831842991</v>
+        <v>6.944228876608308</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.9209439647931161</v>
       </c>
       <c r="JC105" t="n">
-        <v>10.40377846241382</v>
+        <v>6.944229020592215</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.9110100759941124</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC106" t="n">
-        <v>10.40377829569561</v>
+        <v>6.944228853874006</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.9209439647931161</v>
       </c>
       <c r="JC107" t="n">
-        <v>10.40377828811751</v>
+        <v>6.944228846295906</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.9209439647931161</v>
       </c>
       <c r="JC108" t="n">
-        <v>10.40377800014969</v>
+        <v>6.944228558328091</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.9110100759941124</v>
+        <v>1.305315212968727</v>
       </c>
       <c r="JC109" t="n">
-        <v>10.40377801530589</v>
+        <v>6.944228573484292</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.9209439647931161</v>
       </c>
       <c r="JC110" t="n">
-        <v>10.40377824264891</v>
+        <v>6.944228800827304</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.9110100759941124</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC111" t="n">
-        <v>10.4037782274927</v>
+        <v>6.944228785671103</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC112" t="n">
-        <v>10.40377833358611</v>
+        <v>6.944228891764508</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.9209439647931161</v>
       </c>
       <c r="JC113" t="n">
-        <v>10.4037780607745</v>
+        <v>6.944228618952895</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.9110100759941124</v>
+        <v>1.305315212968727</v>
       </c>
       <c r="JC114" t="n">
-        <v>10.4037781592898</v>
+        <v>6.944228717468199</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.9110100759941124</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC115" t="n">
-        <v>10.40377831085181</v>
+        <v>6.944228869030208</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.9110100759941124</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC116" t="n">
-        <v>10.40377832600801</v>
+        <v>6.944228884186408</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.9110100759941124</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC117" t="n">
-        <v>10.40377830327371</v>
+        <v>6.944228861452108</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.9110100759941124</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC118" t="n">
-        <v>10.40377838663281</v>
+        <v>6.944228944811211</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.9209439647931161</v>
       </c>
       <c r="JC119" t="n">
-        <v>10.40377848514812</v>
+        <v>6.944229043326517</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC120" t="n">
-        <v>10.40377831842991</v>
+        <v>6.944228876608308</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.9110100759941124</v>
+        <v>1.305315212968727</v>
       </c>
       <c r="JC121" t="n">
-        <v>10.40377830327371</v>
+        <v>6.944228861452108</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC122" t="n">
-        <v>10.40377827296131</v>
+        <v>6.944228831139705</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC123" t="n">
-        <v>10.40377825780511</v>
+        <v>6.944228815983505</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC124" t="n">
-        <v>10.40377829569561</v>
+        <v>6.944228853874006</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC125" t="n">
-        <v>10.40377831085181</v>
+        <v>6.944228869030208</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC126" t="n">
-        <v>10.40377830327371</v>
+        <v>6.944228861452108</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP-S4_repeat_3_000007.xlsx
+++ b/out/MLP-S4_repeat_3_000007.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245342</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245342</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA4" t="n">
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.9110100759941124</v>
+        <v>0.413893199309912</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>3.50780289896909</v>
+        <v>0.613893199309912</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.3110100759941124</v>
+        <v>0.613893199309912</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.3110100759941124</v>
+        <v>-0.2589783378245342</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245342</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245342</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245342</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245342</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245342</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245342</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245342</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245342</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245342</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245342</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245342</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245342</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245342</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245342</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.9110100759941124</v>
+        <v>0.613893199309912</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>3.50780289896909</v>
+        <v>0.613893199309912</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.3110100759941124</v>
+        <v>0.613893199309912</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.3110100759941124</v>
+        <v>-0.2589783378245342</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.2589783378245342</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245342</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245342</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245342</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245342</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245342</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245342</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245342</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245342</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.9110100759941124</v>
+        <v>0.613893199309912</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>3.50780289896909</v>
+        <v>1.486764736444358</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>3.50780289896909</v>
+        <v>2.359636273578805</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>3.50780289896909</v>
+        <v>2.359636273578805</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,10 +31949,10 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>3.50780289896909</v>
+        <v>2.359636273578805</v>
       </c>
       <c r="JC39" t="n">
-        <v>-0.0003674984412823105</v>
+        <v>-0.0002799414131003432</v>
       </c>
     </row>
     <row r="40">
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>4.236714191927718</v>
+        <v>3.227311046086718</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
@@ -32744,10 +32744,10 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>3.50780289896909</v>
+        <v>2.359636273578805</v>
       </c>
       <c r="JC40" t="n">
-        <v>8.479977730957103</v>
+        <v>6.459610932621909</v>
       </c>
     </row>
     <row r="41">
@@ -33528,7 +33528,7 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.635314214801281</v>
+        <v>0.4839496649807707</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
@@ -33539,10 +33539,10 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>3.50780289896909</v>
+        <v>1.486764736444358</v>
       </c>
       <c r="JC41" t="n">
-        <v>5.508205563908311</v>
+        <v>4.195867766580931</v>
       </c>
     </row>
     <row r="42">
@@ -34323,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.7943494296378657</v>
+        <v>0.6050946050041103</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
@@ -34334,10 +34334,10 @@
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.3110100759941124</v>
+        <v>1.486764736444358</v>
       </c>
       <c r="JC42" t="n">
-        <v>6.461691214287085</v>
+        <v>4.922184120816682</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>1.138696140261829</v>
+        <v>0.8674002466717341</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35129,10 +35129,10 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>2.90780289896909</v>
+        <v>1.286764736444358</v>
       </c>
       <c r="JC43" t="n">
-        <v>7.945182563901387</v>
+        <v>6.052231490823625</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>1.218179665453335</v>
+        <v>0.9279464494843378</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>2.90780289896909</v>
+        <v>2.159636273578804</v>
       </c>
       <c r="JC44" t="n">
-        <v>9.242930328358025</v>
+        <v>7.040788814923783</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>1.291024172150352</v>
+        <v>0.9834354624372812</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>3.50780289896909</v>
+        <v>2.359636273578805</v>
       </c>
       <c r="JC45" t="n">
-        <v>10.60689266345952</v>
+        <v>8.079784984623686</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.5826151974237787</v>
+        <v>0.4438067993660553</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>3.50780289896909</v>
+        <v>1.486764736444358</v>
       </c>
       <c r="JC46" t="n">
-        <v>10.480025906215</v>
+        <v>7.983144413236992</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.2813771541925718</v>
+        <v>0.2143377560575092</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.9110100759941124</v>
+        <v>1.286764736444358</v>
       </c>
       <c r="JC47" t="n">
-        <v>10.45970683448137</v>
+        <v>7.967666408112941</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.1340672239460708</v>
+        <v>0.1021255595201966</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>2.90780289896909</v>
+        <v>0.413893199309912</v>
       </c>
       <c r="JC48" t="n">
-        <v>10.44624190243252</v>
+        <v>7.957409496577272</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.03972318327363588</v>
+        <v>0.03025909091229656</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.9110100759941124</v>
+        <v>0.413893199309912</v>
       </c>
       <c r="JC49" t="n">
-        <v>10.39147773795493</v>
+        <v>7.915692835710553</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.02627540443743448</v>
+        <v>0.02001574073903093</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245342</v>
       </c>
       <c r="JC50" t="n">
-        <v>10.40428485737099</v>
+        <v>7.925448699995566</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.01344763436557187</v>
+        <v>0.01024190859296851</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245342</v>
       </c>
       <c r="JC51" t="n">
-        <v>10.40488512594918</v>
+        <v>7.925904757470457</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.006876542371678241</v>
+        <v>0.005236689749755501</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245342</v>
       </c>
       <c r="JC52" t="n">
-        <v>10.40518257374426</v>
+        <v>7.926130155522045</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.002582032646931447</v>
+        <v>0.001965928324344496</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245342</v>
       </c>
       <c r="JC53" t="n">
-        <v>10.40346488316397</v>
+        <v>7.924820343857011</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.001404935215134951</v>
+        <v>0.0010691577823907</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245342</v>
       </c>
       <c r="JC54" t="n">
-        <v>10.40369127978369</v>
+        <v>7.924991633148337</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0006736993777768125</v>
+        <v>0.0005123691978134717</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245342</v>
       </c>
       <c r="JC55" t="n">
-        <v>10.40363364700469</v>
+        <v>7.924946534546754</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.0004151488351447622</v>
+        <v>0.0003147854131663881</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245342</v>
       </c>
       <c r="JC56" t="n">
-        <v>10.40379011738283</v>
+        <v>7.925064478802144</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.0002152849997018866</v>
+        <v>0.0001627871726701286</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.9110100759941124</v>
+        <v>0.613893199309912</v>
       </c>
       <c r="JC57" t="n">
-        <v>10.40380430991044</v>
+        <v>7.925074097409619</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.000101902964994014</v>
+        <v>7.592654359359939e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>3.50780289896909</v>
+        <v>1.486764736444358</v>
       </c>
       <c r="JC58" t="n">
-        <v>10.40379269293151</v>
+        <v>7.925064057982327</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>6.279475802142372e-05</v>
+        <v>4.744500148827117e-05</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>3.50780289896909</v>
+        <v>1.486764736444358</v>
       </c>
       <c r="JC59" t="n">
-        <v>10.40381761234375</v>
+        <v>7.925081986282775</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>2.647150449619047e-05</v>
+        <v>1.831222555273368e-05</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.3110100759941124</v>
+        <v>0.613893199309912</v>
       </c>
       <c r="JC60" t="n">
-        <v>10.40380643584548</v>
+        <v>7.925072297427367</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>8.38179904731087e-06</v>
+        <v>5.293691574854516e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.3110100759941124</v>
+        <v>-0.2589783378245342</v>
       </c>
       <c r="JC61" t="n">
-        <v>10.40379773660624</v>
+        <v>7.925064420380455</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>2.788397616378431e-06</v>
+        <v>5.63141154556023e-07</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245342</v>
       </c>
       <c r="JC62" t="n">
-        <v>10.40379389416601</v>
+        <v>7.925060330567965</v>
       </c>
     </row>
     <row r="63">
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245342</v>
       </c>
       <c r="JC63" t="n">
-        <v>10.40378788273942</v>
+        <v>7.925054463125281</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>-3.107779831880603e-06</v>
+        <v>-4.053889915940302e-06</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.9110100759941124</v>
+        <v>0.413893199309912</v>
       </c>
       <c r="JC64" t="n">
-        <v>10.40378278949728</v>
+        <v>7.925049393769912</v>
       </c>
     </row>
     <row r="65">
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>3.50780289896909</v>
+        <v>1.486764736444358</v>
       </c>
       <c r="JC65" t="n">
-        <v>10.40377842452332</v>
+        <v>7.925045028795944</v>
       </c>
     </row>
     <row r="66">
@@ -53414,10 +53414,10 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>3.50780289896909</v>
+        <v>2.359636273578805</v>
       </c>
       <c r="JC66" t="n">
-        <v>10.40377951576977</v>
+        <v>7.9250461200424</v>
       </c>
     </row>
     <row r="67">
@@ -54209,10 +54209,10 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>3.50780289896909</v>
+        <v>1.486764736444358</v>
       </c>
       <c r="JC67" t="n">
-        <v>10.40377882616264</v>
+        <v>7.925045430435264</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.3110100759941124</v>
+        <v>0.613893199309912</v>
       </c>
       <c r="JC68" t="n">
-        <v>10.40377885647504</v>
+        <v>7.925045460747667</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.3110100759941124</v>
+        <v>-0.4589783378245342</v>
       </c>
       <c r="JC69" t="n">
-        <v>10.40377866702253</v>
+        <v>7.925045271295156</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245342</v>
       </c>
       <c r="JC70" t="n">
-        <v>10.40377872006923</v>
+        <v>7.92504532434186</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245342</v>
       </c>
       <c r="JC71" t="n">
-        <v>10.40377877311593</v>
+        <v>7.925045377388561</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245342</v>
       </c>
       <c r="JC72" t="n">
-        <v>10.40377873522543</v>
+        <v>7.92504533949806</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245342</v>
       </c>
       <c r="JC73" t="n">
-        <v>10.40377860639773</v>
+        <v>7.925045210670354</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245342</v>
       </c>
       <c r="JC74" t="n">
-        <v>10.40377846241382</v>
+        <v>7.925045066686446</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245342</v>
       </c>
       <c r="JC75" t="n">
-        <v>10.40377830327371</v>
+        <v>7.925044907546337</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245342</v>
       </c>
       <c r="JC76" t="n">
-        <v>10.40377835632041</v>
+        <v>7.925044960593041</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245342</v>
       </c>
       <c r="JC77" t="n">
-        <v>10.40377830327371</v>
+        <v>7.925044907546337</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245342</v>
       </c>
       <c r="JC78" t="n">
-        <v>10.40377830327371</v>
+        <v>7.925044907546337</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245342</v>
       </c>
       <c r="JC79" t="n">
-        <v>10.4037781213993</v>
+        <v>7.925044725671929</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245342</v>
       </c>
       <c r="JC80" t="n">
-        <v>10.40377828811751</v>
+        <v>7.925044892390138</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245342</v>
       </c>
       <c r="JC81" t="n">
-        <v>10.40377848514812</v>
+        <v>7.925045089420747</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245342</v>
       </c>
       <c r="JC82" t="n">
-        <v>10.40377832600801</v>
+        <v>7.925044930280639</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245342</v>
       </c>
       <c r="JC83" t="n">
-        <v>10.40377836389851</v>
+        <v>7.92504496817114</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245342</v>
       </c>
       <c r="JC84" t="n">
-        <v>10.40377856092912</v>
+        <v>7.925045165201752</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245342</v>
       </c>
       <c r="JC85" t="n">
-        <v>10.40377853819482</v>
+        <v>7.92504514246745</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245342</v>
       </c>
       <c r="JC86" t="n">
-        <v>10.40377838663281</v>
+        <v>7.925044990905441</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245342</v>
       </c>
       <c r="JC87" t="n">
-        <v>10.40377831085181</v>
+        <v>7.925044915124439</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.9110100759941124</v>
+        <v>0.613893199309912</v>
       </c>
       <c r="JC88" t="n">
-        <v>10.40377840936711</v>
+        <v>7.925045013639743</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>1</v>
       </c>
       <c r="JB89" t="n">
-        <v>3.50780289896909</v>
+        <v>0.613893199309912</v>
       </c>
       <c r="JC89" t="n">
-        <v>10.40377841694522</v>
+        <v>7.925045021217843</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.3110100759941124</v>
+        <v>0.613893199309912</v>
       </c>
       <c r="JC90" t="n">
-        <v>10.40377868217873</v>
+        <v>7.925045286451357</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.3110100759941124</v>
+        <v>-0.2589783378245342</v>
       </c>
       <c r="JC91" t="n">
-        <v>10.40377838663281</v>
+        <v>7.925044990905441</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.2589783378245342</v>
       </c>
       <c r="JC92" t="n">
-        <v>10.40377862913203</v>
+        <v>7.925045233404655</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.9110100759941124</v>
+        <v>0.413893199309912</v>
       </c>
       <c r="JC93" t="n">
-        <v>10.40377871249113</v>
+        <v>7.925045316763758</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>3.50780289896909</v>
+        <v>0.613893199309912</v>
       </c>
       <c r="JC94" t="n">
-        <v>10.40377854577292</v>
+        <v>7.925045150045549</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.3110100759941124</v>
+        <v>0.613893199309912</v>
       </c>
       <c r="JC95" t="n">
-        <v>10.40377873522543</v>
+        <v>7.92504533949806</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.3110100759941124</v>
+        <v>-0.2589783378245342</v>
       </c>
       <c r="JC96" t="n">
-        <v>10.40377838663281</v>
+        <v>7.925044990905441</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245342</v>
       </c>
       <c r="JC97" t="n">
-        <v>10.4037781820241</v>
+        <v>7.925044786296731</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245342</v>
       </c>
       <c r="JC98" t="n">
-        <v>10.40377829569561</v>
+        <v>7.925044899968237</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245342</v>
       </c>
       <c r="JC99" t="n">
-        <v>10.40377831085181</v>
+        <v>7.925044915124439</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245342</v>
       </c>
       <c r="JC100" t="n">
-        <v>10.4037780759307</v>
+        <v>7.925044680203326</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245342</v>
       </c>
       <c r="JC101" t="n">
-        <v>10.4037781365555</v>
+        <v>7.925044740828128</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245342</v>
       </c>
       <c r="JC102" t="n">
-        <v>10.40377800772779</v>
+        <v>7.925044612000423</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245342</v>
       </c>
       <c r="JC103" t="n">
-        <v>10.4037781441336</v>
+        <v>7.925044748406229</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245342</v>
       </c>
       <c r="JC104" t="n">
-        <v>10.40377831842991</v>
+        <v>7.925044922702538</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245342</v>
       </c>
       <c r="JC105" t="n">
-        <v>10.40377846241382</v>
+        <v>7.925045066686446</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245342</v>
       </c>
       <c r="JC106" t="n">
-        <v>10.40377829569561</v>
+        <v>7.925044899968237</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245342</v>
       </c>
       <c r="JC107" t="n">
-        <v>10.40377828811751</v>
+        <v>7.925044892390138</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245342</v>
       </c>
       <c r="JC108" t="n">
-        <v>10.40377800014969</v>
+        <v>7.925044604422322</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245342</v>
       </c>
       <c r="JC109" t="n">
-        <v>10.40377801530589</v>
+        <v>7.925044619578522</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245342</v>
       </c>
       <c r="JC110" t="n">
-        <v>10.40377824264891</v>
+        <v>7.925044846921535</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245342</v>
       </c>
       <c r="JC111" t="n">
-        <v>10.4037782274927</v>
+        <v>7.925044831765333</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245342</v>
       </c>
       <c r="JC112" t="n">
-        <v>10.40377833358611</v>
+        <v>7.92504493785874</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245342</v>
       </c>
       <c r="JC113" t="n">
-        <v>10.4037780607745</v>
+        <v>7.925044665047124</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245342</v>
       </c>
       <c r="JC114" t="n">
-        <v>10.4037781592898</v>
+        <v>7.92504476356243</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245342</v>
       </c>
       <c r="JC115" t="n">
-        <v>10.40377831085181</v>
+        <v>7.925044915124439</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245342</v>
       </c>
       <c r="JC116" t="n">
-        <v>10.40377832600801</v>
+        <v>7.925044930280639</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245342</v>
       </c>
       <c r="JC117" t="n">
-        <v>10.40377830327371</v>
+        <v>7.925044907546337</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245342</v>
       </c>
       <c r="JC118" t="n">
-        <v>10.40377838663281</v>
+        <v>7.925044990905441</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245342</v>
       </c>
       <c r="JC119" t="n">
-        <v>10.40377848514812</v>
+        <v>7.925045089420747</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245342</v>
       </c>
       <c r="JC120" t="n">
-        <v>10.40377831842991</v>
+        <v>7.925044922702538</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245342</v>
       </c>
       <c r="JC121" t="n">
-        <v>10.40377830327371</v>
+        <v>7.925044907546337</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245342</v>
       </c>
       <c r="JC122" t="n">
-        <v>10.40377827296131</v>
+        <v>7.925044877233936</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245342</v>
       </c>
       <c r="JC123" t="n">
-        <v>10.40377825780511</v>
+        <v>7.925044862077735</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245342</v>
       </c>
       <c r="JC124" t="n">
-        <v>10.40377829569561</v>
+        <v>7.925044899968237</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245342</v>
       </c>
       <c r="JC125" t="n">
-        <v>10.40377831085181</v>
+        <v>7.925044915124439</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.9110100759941124</v>
+        <v>-0.4589783378245342</v>
       </c>
       <c r="JC126" t="n">
-        <v>10.40377830327371</v>
+        <v>7.925044907546337</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP-S4_repeat_3_000007.xlsx
+++ b/out/MLP-S4_repeat_3_000007.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>0.3992772698402405</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.4589783378245342</v>
+        <v>-1.28</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>0.4100438952445984</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.4589783378245342</v>
+        <v>-0.8599999999999997</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>0.4004988968372345</v>
       </c>
       <c r="JB4" t="n">
-        <v>0.413893199309912</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0.5474867224693298</v>
       </c>
       <c r="JB5" t="n">
-        <v>0.613893199309912</v>
+        <v>-0.3</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>0.4751985669136047</v>
       </c>
       <c r="JB6" t="n">
-        <v>0.613893199309912</v>
+        <v>-0.3</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>0.4198531806468964</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.2589783378245342</v>
+        <v>0.3</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>0.3980597257614136</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.4589783378245342</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>0.4124477505683899</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.4589783378245342</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>0.4151072800159454</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.4589783378245342</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>0.4173382818698883</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.4589783378245342</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>0.4078379273414612</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.4589783378245342</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>0.3971682488918304</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.4589783378245342</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>0.4323987364768982</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.4589783378245342</v>
+        <v>0.3</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>0.4236037135124207</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.4589783378245342</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>0.4492195844650269</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.4589783378245342</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>0.4287806153297424</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.4589783378245342</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>0.4362541437149048</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.4589783378245342</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>0.4223402440547943</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.4589783378245342</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>0.4529329538345337</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.4589783378245342</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0</v>
+        <v>0.4621348083019257</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.4589783378245342</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>0.4983124732971191</v>
       </c>
       <c r="JB22" t="n">
-        <v>0.613893199309912</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0.570509135723114</v>
       </c>
       <c r="JB23" t="n">
-        <v>0.613893199309912</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>0.4968133568763733</v>
       </c>
       <c r="JB24" t="n">
-        <v>0.613893199309912</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0</v>
+        <v>0.4609841704368591</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.2589783378245342</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>0.4573456346988678</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.2589783378245342</v>
+        <v>-0.16</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>0.4470368921756744</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.4589783378245342</v>
+        <v>-0.3</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0</v>
+        <v>0.4311650395393372</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.4589783378245342</v>
+        <v>-0.3</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>0.4847642183303833</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.4589783378245342</v>
+        <v>-0.3</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>0.4680669605731964</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.4589783378245342</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>0.4548905789852142</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.4589783378245342</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>0.4380259215831757</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.4589783378245342</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>0.4376643598079681</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.4589783378245342</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>0.4480449259281158</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.4589783378245342</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0</v>
+        <v>0.451367974281311</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.613893199309912</v>
+        <v>-0.16</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0.5492212176322937</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.486764736444358</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0.7424517869949341</v>
       </c>
       <c r="JB37" t="n">
-        <v>2.359636273578805</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0.6321655511856079</v>
       </c>
       <c r="JB38" t="n">
-        <v>2.359636273578805</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,13 +31946,13 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0.5899713635444641</v>
       </c>
       <c r="JB39" t="n">
-        <v>2.359636273578805</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC39" t="n">
-        <v>-0.0002799414131003432</v>
+        <v>-0.0001655819800505415</v>
       </c>
     </row>
     <row r="40">
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>3.227311046086718</v>
+        <v>1.908915605419707</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
@@ -32741,13 +32741,13 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0.5725860595703125</v>
       </c>
       <c r="JB40" t="n">
-        <v>2.359636273578805</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC40" t="n">
-        <v>6.459610932621909</v>
+        <v>3.820782201421234</v>
       </c>
     </row>
     <row r="41">
@@ -33528,7 +33528,7 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.4839496649807707</v>
+        <v>0.2862504102768729</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
@@ -33536,13 +33536,13 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.5461211800575256</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.486764736444358</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC41" t="n">
-        <v>4.195867766580931</v>
+        <v>2.481805283148065</v>
       </c>
     </row>
     <row r="42">
@@ -34323,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.6050946050041103</v>
+        <v>0.3579062094468367</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
@@ -34331,13 +34331,13 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0</v>
+        <v>0.4929031431674957</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.486764736444358</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC42" t="n">
-        <v>4.922184120816682</v>
+        <v>2.911412704952789</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.8674002466717341</v>
+        <v>0.5130568539070393</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35126,13 +35126,13 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.6140757203102112</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.286764736444358</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC43" t="n">
-        <v>6.052231490823625</v>
+        <v>3.579822185635244</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.9279464494843378</v>
+        <v>0.5488688594293036</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.6730546951293945</v>
       </c>
       <c r="JB44" t="n">
-        <v>2.159636273578804</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC44" t="n">
-        <v>7.040788814923783</v>
+        <v>4.164541999836108</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.9834354624372812</v>
+        <v>0.5816910990992846</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.7257717251777649</v>
       </c>
       <c r="JB45" t="n">
-        <v>2.359636273578805</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC45" t="n">
-        <v>8.079784984623686</v>
+        <v>4.779096175439199</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.4438067993660553</v>
+        <v>0.2625057084191442</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0.7869086265563965</v>
       </c>
       <c r="JB46" t="n">
-        <v>1.486764736444358</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC46" t="n">
-        <v>7.983144413236992</v>
+        <v>4.721934442921425</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.2143377560575092</v>
+        <v>0.1267789021009197</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0</v>
+        <v>0.4831127822399139</v>
       </c>
       <c r="JB47" t="n">
-        <v>1.286764736444358</v>
+        <v>-0.3</v>
       </c>
       <c r="JC47" t="n">
-        <v>7.967666408112941</v>
+        <v>4.712779365589396</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.1021255595201966</v>
+        <v>0.06040575950735491</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0.5719237327575684</v>
       </c>
       <c r="JB48" t="n">
-        <v>0.413893199309912</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC48" t="n">
-        <v>7.957409496577272</v>
+        <v>4.706712529200177</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.03025909091229656</v>
+        <v>0.01789816837695915</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>0.4183266758918762</v>
       </c>
       <c r="JB49" t="n">
-        <v>0.413893199309912</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC49" t="n">
-        <v>7.915692835710553</v>
+        <v>4.682037535803007</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.02001574073903093</v>
+        <v>0.01183757656008916</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>0.4125411212444305</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.4589783378245342</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC50" t="n">
-        <v>7.925448699995566</v>
+        <v>4.687806569566344</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.01024190859296851</v>
+        <v>0.006056163523399848</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>0.3421301245689392</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.4589783378245342</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC51" t="n">
-        <v>7.925904757470457</v>
+        <v>4.688074276883612</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.005236689749755501</v>
+        <v>0.003095519383377557</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>0.3974525332450867</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.4589783378245342</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC52" t="n">
-        <v>7.926130155522045</v>
+        <v>4.68820554651627</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.001965928324344496</v>
+        <v>0.001160602772461799</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>0.3782422840595245</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.4589783378245342</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC53" t="n">
-        <v>7.924820343857011</v>
+        <v>4.687428883703615</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0010691577823907</v>
+        <v>0.0006302546024891238</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>0.3438355326652527</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.4589783378245342</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC54" t="n">
-        <v>7.924991633148337</v>
+        <v>4.687528140811389</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0005123691978134717</v>
+        <v>0.0003009710309649564</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>0.3700179755687714</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.4589783378245342</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC55" t="n">
-        <v>7.924946534546754</v>
+        <v>4.687499426584645</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.0003147854131663881</v>
+        <v>0.0001839193825475277</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>0.3895614743232727</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.4589783378245342</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC56" t="n">
-        <v>7.925064478802144</v>
+        <v>4.687567135797627</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.0001627871726701286</v>
+        <v>9.381943911860337e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>0.2898998558521271</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.613893199309912</v>
+        <v>0.16</v>
       </c>
       <c r="JC57" t="n">
-        <v>7.925074097409619</v>
+        <v>4.68757079099824</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>7.592654359359939e-05</v>
+        <v>4.295647027768853e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0.714535653591156</v>
       </c>
       <c r="JB58" t="n">
-        <v>1.486764736444358</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC58" t="n">
-        <v>7.925064057982327</v>
+        <v>4.687562792321457</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>4.744500148827117e-05</v>
+        <v>2.569951306630508e-05</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0.5370056629180908</v>
       </c>
       <c r="JB59" t="n">
-        <v>1.486764736444358</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC59" t="n">
-        <v>7.925081986282775</v>
+        <v>4.687571494155336</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>1.831222555273368e-05</v>
+        <v>8.987335331640211e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>0.3370346128940582</v>
       </c>
       <c r="JB60" t="n">
-        <v>0.613893199309912</v>
+        <v>0.16</v>
       </c>
       <c r="JC60" t="n">
-        <v>7.925072297427367</v>
+        <v>4.687563635373489</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>5.293691574854516e-06</v>
+        <v>1.176214944912711e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>0.3252421617507935</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.2589783378245342</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC61" t="n">
-        <v>7.925064420380455</v>
+        <v>4.687556854583018</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>5.63141154556023e-07</v>
+        <v>-1.662115307266386e-06</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>0.3195320963859558</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.4589783378245342</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC62" t="n">
-        <v>7.925060330567965</v>
+        <v>4.687552434039168</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>-2.093548687745288e-06</v>
+        <v>-3.062365791830193e-06</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>0.3497939705848694</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.4589783378245342</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC63" t="n">
-        <v>7.925054463125281</v>
+        <v>4.687546855744045</v>
       </c>
     </row>
     <row r="64">
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>0.4168807566165924</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.413893199309912</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC64" t="n">
-        <v>7.925049393769912</v>
+        <v>4.687541809122977</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>-3.735991635587426e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0.6911961436271667</v>
       </c>
       <c r="JB65" t="n">
-        <v>1.486764736444358</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC65" t="n">
-        <v>7.925045028795944</v>
+        <v>4.687542127403193</v>
       </c>
     </row>
     <row r="66">
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0.9258518218994141</v>
       </c>
       <c r="JB66" t="n">
-        <v>2.359636273578805</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC66" t="n">
-        <v>7.9250461200424</v>
+        <v>4.68754321864965</v>
       </c>
     </row>
     <row r="67">
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0.7316135168075562</v>
       </c>
       <c r="JB67" t="n">
-        <v>1.486764736444358</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC67" t="n">
-        <v>7.925045430435264</v>
+        <v>4.687542529042514</v>
       </c>
     </row>
     <row r="68">
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>0.4439457058906555</v>
       </c>
       <c r="JB68" t="n">
-        <v>0.613893199309912</v>
+        <v>0.16</v>
       </c>
       <c r="JC68" t="n">
-        <v>7.925045460747667</v>
+        <v>4.687542559354916</v>
       </c>
     </row>
     <row r="69">
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>0.3451406955718994</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.4589783378245342</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC69" t="n">
-        <v>7.925045271295156</v>
+        <v>4.687542369902406</v>
       </c>
     </row>
     <row r="70">
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>0.3135860562324524</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.4589783378245342</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC70" t="n">
-        <v>7.92504532434186</v>
+        <v>4.687542422949109</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>0.217247411608696</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.4589783378245342</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC71" t="n">
-        <v>7.925045377388561</v>
+        <v>4.687542475995811</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>0.2168978154659271</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.4589783378245342</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC72" t="n">
-        <v>7.92504533949806</v>
+        <v>4.687542438105309</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>0.2685770094394684</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.4589783378245342</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC73" t="n">
-        <v>7.925045210670354</v>
+        <v>4.687542309277602</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>0.2560635805130005</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.4589783378245342</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC74" t="n">
-        <v>7.925045066686446</v>
+        <v>4.687542165293696</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>0.2531095445156097</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.4589783378245342</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC75" t="n">
-        <v>7.925044907546337</v>
+        <v>4.687542006153588</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>0.3048538565635681</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.4589783378245342</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC76" t="n">
-        <v>7.925044960593041</v>
+        <v>4.68754205920029</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>0.2469112724065781</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.4589783378245342</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC77" t="n">
-        <v>7.925044907546337</v>
+        <v>4.687542006153588</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>0.2775193750858307</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.4589783378245342</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC78" t="n">
-        <v>7.925044907546337</v>
+        <v>4.687542006153588</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>0.3475234806537628</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.4589783378245342</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC79" t="n">
-        <v>7.925044725671929</v>
+        <v>4.687541824279178</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>0.3360974788665771</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.4589783378245342</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC80" t="n">
-        <v>7.925044892390138</v>
+        <v>4.687541990997386</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>0.2777099609375</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.4589783378245342</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC81" t="n">
-        <v>7.925045089420747</v>
+        <v>4.687542188027996</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>0.2013833224773407</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.4589783378245342</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC82" t="n">
-        <v>7.925044930280639</v>
+        <v>4.687542028887888</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>0.2892187535762787</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.4589783378245342</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC83" t="n">
-        <v>7.92504496817114</v>
+        <v>4.68754206677839</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>0.4336974918842316</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.4589783378245342</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC84" t="n">
-        <v>7.925045165201752</v>
+        <v>4.687542263809</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>0.3188727498054504</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.4589783378245342</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC85" t="n">
-        <v>7.92504514246745</v>
+        <v>4.687542241074699</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>0.3003447651863098</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.4589783378245342</v>
+        <v>0.16</v>
       </c>
       <c r="JC86" t="n">
-        <v>7.925044990905441</v>
+        <v>4.687542089512691</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>0.3620555996894836</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.4589783378245342</v>
+        <v>0.16</v>
       </c>
       <c r="JC87" t="n">
-        <v>7.925044915124439</v>
+        <v>4.687542013731687</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0</v>
+        <v>0.3940849900245667</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.613893199309912</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC88" t="n">
-        <v>7.925045013639743</v>
+        <v>4.687542112246993</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0.5246185064315796</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.613893199309912</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC89" t="n">
-        <v>7.925045021217843</v>
+        <v>4.687542119825094</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>0.4229021668434143</v>
       </c>
       <c r="JB90" t="n">
-        <v>0.613893199309912</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC90" t="n">
-        <v>7.925045286451357</v>
+        <v>4.687542385058607</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>0.3979296386241913</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.2589783378245342</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC91" t="n">
-        <v>7.925044990905441</v>
+        <v>4.687542089512691</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>0.4793009757995605</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.2589783378245342</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC92" t="n">
-        <v>7.925045233404655</v>
+        <v>4.687542332011904</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>0.3613139986991882</v>
       </c>
       <c r="JB93" t="n">
-        <v>0.413893199309912</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC93" t="n">
-        <v>7.925045316763758</v>
+        <v>4.687542415371008</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0.6009055376052856</v>
       </c>
       <c r="JB94" t="n">
-        <v>0.613893199309912</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC94" t="n">
-        <v>7.925045150045549</v>
+        <v>4.6875422486528</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>0.4212439060211182</v>
       </c>
       <c r="JB95" t="n">
-        <v>0.613893199309912</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC95" t="n">
-        <v>7.92504533949806</v>
+        <v>4.687542438105309</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>0.3713493943214417</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.2589783378245342</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC96" t="n">
-        <v>7.925044990905441</v>
+        <v>4.687542089512691</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>0.3054653406143188</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.4589783378245342</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC97" t="n">
-        <v>7.925044786296731</v>
+        <v>4.687541884903981</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>0.2828274667263031</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.4589783378245342</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC98" t="n">
-        <v>7.925044899968237</v>
+        <v>4.687541998575486</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>0.3803276717662811</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.4589783378245342</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC99" t="n">
-        <v>7.925044915124439</v>
+        <v>4.687542013731687</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>0.3303030133247375</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.4589783378245342</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC100" t="n">
-        <v>7.925044680203326</v>
+        <v>4.687541778810576</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>0.3147154748439789</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.4589783378245342</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC101" t="n">
-        <v>7.925044740828128</v>
+        <v>4.687541839435378</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>0.3060348331928253</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.4589783378245342</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC102" t="n">
-        <v>7.925044612000423</v>
+        <v>4.687541710607671</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>0.4614903628826141</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.4589783378245342</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC103" t="n">
-        <v>7.925044748406229</v>
+        <v>4.687541847013479</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>0.3863776028156281</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.4589783378245342</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC104" t="n">
-        <v>7.925044922702538</v>
+        <v>4.687542021309787</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>0.3204273581504822</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.4589783378245342</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC105" t="n">
-        <v>7.925045066686446</v>
+        <v>4.687542165293696</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>0.3948009312152863</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.4589783378245342</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC106" t="n">
-        <v>7.925044899968237</v>
+        <v>4.687541998575486</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>0.3788037002086639</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.4589783378245342</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC107" t="n">
-        <v>7.925044892390138</v>
+        <v>4.687541990997386</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>0.2789621949195862</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.4589783378245342</v>
+        <v>0.16</v>
       </c>
       <c r="JC108" t="n">
-        <v>7.925044604422322</v>
+        <v>4.687541703029571</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>0.3557459115982056</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.4589783378245342</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC109" t="n">
-        <v>7.925044619578522</v>
+        <v>4.687541718185773</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>0.3423918187618256</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.4589783378245342</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC110" t="n">
-        <v>7.925044846921535</v>
+        <v>4.687541945528784</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>0.4224537312984467</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.4589783378245342</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC111" t="n">
-        <v>7.925044831765333</v>
+        <v>4.687541930372583</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>0.3655299842357635</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.4589783378245342</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC112" t="n">
-        <v>7.92504493785874</v>
+        <v>4.687542036465988</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>0.362040638923645</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.4589783378245342</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC113" t="n">
-        <v>7.925044665047124</v>
+        <v>4.687541763654375</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>0.4155237972736359</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.4589783378245342</v>
+        <v>0.3</v>
       </c>
       <c r="JC114" t="n">
-        <v>7.92504476356243</v>
+        <v>4.687541862169679</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>0.3947356343269348</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.4589783378245342</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC115" t="n">
-        <v>7.925044915124439</v>
+        <v>4.687542013731687</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>0.4122743606567383</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.4589783378245342</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC116" t="n">
-        <v>7.925044930280639</v>
+        <v>4.687542028887888</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>0.435932993888855</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.4589783378245342</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC117" t="n">
-        <v>7.925044907546337</v>
+        <v>4.687542006153588</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>0.4511317312717438</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.4589783378245342</v>
+        <v>0.3</v>
       </c>
       <c r="JC118" t="n">
-        <v>7.925044990905441</v>
+        <v>4.687542089512691</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>0.3733265101909637</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.4589783378245342</v>
+        <v>0.16</v>
       </c>
       <c r="JC119" t="n">
-        <v>7.925045089420747</v>
+        <v>4.687542188027996</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>0.3546121418476105</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.4589783378245342</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC120" t="n">
-        <v>7.925044922702538</v>
+        <v>4.687542021309787</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>0.3751132488250732</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.4589783378245342</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC121" t="n">
-        <v>7.925044907546337</v>
+        <v>4.687542006153588</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>0.3958082497119904</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.4589783378245342</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC122" t="n">
-        <v>7.925044877233936</v>
+        <v>4.687541975841185</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>0.3725690245628357</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.4589783378245342</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC123" t="n">
-        <v>7.925044862077735</v>
+        <v>4.687541960684985</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>0.3747598528862</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.4589783378245342</v>
+        <v>-0.16</v>
       </c>
       <c r="JC124" t="n">
-        <v>7.925044899968237</v>
+        <v>4.687541998575486</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>0.4063034653663635</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.4589783378245342</v>
+        <v>0.7200000000000002</v>
       </c>
       <c r="JC125" t="n">
-        <v>7.925044915124439</v>
+        <v>4.687542013731687</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>0.4412351846694946</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.4589783378245342</v>
+        <v>1</v>
       </c>
       <c r="JC126" t="n">
-        <v>7.925044907546337</v>
+        <v>4.687542006153588</v>
       </c>
     </row>
   </sheetData>
